--- a/tmp_export_test/test.xlsx
+++ b/tmp_export_test/test.xlsx
@@ -8,6 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Phase4 Timetable" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CSE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BBA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ECE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ARC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="BFA" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,7 +50,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -69,7 +74,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00F9CB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -79,11 +84,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -105,11 +120,55 @@
         <color rgb="00444444"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00444444"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00444444"/>
+      </right>
+      <top style="thin">
+        <color rgb="00444444"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00444444"/>
+      </right>
+      <top style="thin">
+        <color rgb="00444444"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00444444"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00444444"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00444444"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -123,7 +182,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -132,11 +191,23 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -504,12 +575,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -539,7 +614,27 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRE-A </t>
+          <t>PRE-A  (ARC, BFA, CSE)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>A (BBA, CSE, ECE)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>B (ARC, BBA)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>B2 (ECE)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>C (BFA, ECE)</t>
         </is>
       </c>
     </row>
@@ -559,24 +654,1128 @@
           <t>Academic English 36_Tuấn_Room: C1 - 232</t>
         </is>
       </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>IELTS 4_Terrence_Room: LH - 418</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>German 1_Ms. Son_Room: LH - 417</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Lunch break</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n"/>
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
     </row>
     <row r="7" ht="78" customHeight="1">
-      <c r="A7" s="8" t="n"/>
+      <c r="A7" s="10" t="n"/>
       <c r="B7" s="6" t="inlineStr">
         <is>
           <t>13.00 - 16.15</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="12" t="n"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Business administration_[CSE]_Tuấn_Room: LH - 325</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+    </row>
+    <row r="10" ht="78" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>German 1_Ms. Son_Room: LH - 417</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Architectural Representation &amp; Fabrication_[ARC]_Vạn Lịch/ Bích Huệ_Room: LH - 418</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="78" customHeight="1">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Basic Engineering Concept_[ECE]_Mr. Rocke_Room: LH - 618</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="78" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Elective 101_Ms. Son_Room: LH - 611         (75 seats)</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="78" customHeight="1">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="78" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="78" customHeight="1">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="78" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="78" customHeight="1">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Teacher load summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Teacher</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Taught timeslots</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ms. Son</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tuấn</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Mr. Rocke</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Tân</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Terrence</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Vạn Lịch/ Bích Huệ</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="26">
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B24"/>
+    <mergeCell ref="B5"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B22"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B18"/>
+    <mergeCell ref="B21"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="B19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Foundation Year 2025/26: Semester 2 - Phase 4 - CSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Interactive export with required blocks on top and shared/program/elective strips below (Study programs: CSE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>PRE-A  (ARC, BFA, CSE)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>A (BBA, CSE, ECE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>MONDAY</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Academic English 36_Tuấn_Room: C1 - 232</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>IELTS 4_Terrence_Room: LH - 418</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="78" customHeight="1">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Business administration_[CSE]_Tuấn_Room: LH - 325</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="78" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="78" customHeight="1">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+    </row>
+    <row r="12" ht="78" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="78" customHeight="1">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+    </row>
+    <row r="15" ht="78" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="78" customHeight="1">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="78" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="78" customHeight="1">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Teacher load summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Teacher</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Taught timeslots</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tuấn</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Terrence</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B9"/>
+    <mergeCell ref="B15"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B20"/>
+    <mergeCell ref="B5"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B12"/>
+    <mergeCell ref="B18"/>
+    <mergeCell ref="B11"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="B14"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B17"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A18:A20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Foundation Year 2025/26: Semester 2 - Phase 4 - BBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Interactive export with required blocks on top and shared/program/elective strips below (Study programs: BBA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>A (BBA, CSE, ECE)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>B (ARC, BBA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>MONDAY</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>IELTS 4_Terrence_Room: LH - 418</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>German 1_Ms. Son_Room: LH - 417</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="78" customHeight="1">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Business IT2_[BBA]_Tân_Room: LH - 417</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="78" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="78" customHeight="1">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+    </row>
+    <row r="12" ht="78" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Elective 101_Ms. Son_Room: LH - 611         (75 seats)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="78" customHeight="1">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="78" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="78" customHeight="1">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="78" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="78" customHeight="1">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Teacher load summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Teacher</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Taught timeslots</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ms. Son</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tân</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Terrence</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B9"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B15"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B5"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B16"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B18"/>
+    <mergeCell ref="B21"/>
+    <mergeCell ref="B11"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="D13"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Foundation Year 2025/26: Semester 2 - Phase 4 - ECE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Interactive export with required blocks on top and shared/program/elective strips below (Study programs: ECE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>A (BBA, CSE, ECE)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>B2 (ECE)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>C (BFA, ECE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>MONDAY</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>IELTS 4_Terrence_Room: LH - 418</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="78" customHeight="1">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
     </row>
     <row r="8" ht="78" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -589,171 +1788,901 @@
           <t>8.45 - 12.00</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>German 1_Ms. Son_Room: LH - 417</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Lunch break</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n"/>
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
     </row>
     <row r="10" ht="78" customHeight="1">
-      <c r="A10" s="8" t="n"/>
+      <c r="A10" s="10" t="n"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
           <t>13.00 - 16.15</t>
         </is>
       </c>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Basic Engineering Concept_[ECE]_Mr. Rocke_Room: LH - 618</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="78" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Elective 101_Ms. Son_Room: LH - 611         (75 seats)</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="78" customHeight="1">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="78" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="78" customHeight="1">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="78" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="78" customHeight="1">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Teacher load summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Teacher</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Taught timeslots</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ms. Son</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mr. Rocke</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Terrence</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B15"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B5"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B7"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B16"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B18"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B21"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B8"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Foundation Year 2025/26: Semester 2 - Phase 4 - ARC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Interactive export with required blocks on top and shared/program/elective strips below (Study programs: ARC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>PRE-A  (ARC, BFA, CSE)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>B (ARC, BBA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>MONDAY</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Academic English 36_Tuấn_Room: C1 - 232</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>German 1_Ms. Son_Room: LH - 417</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="78" customHeight="1">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+    </row>
+    <row r="8" ht="78" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Architectural Representation &amp; Fabrication_[ARC]_Vạn Lịch/ Bích Huệ_Room: LH - 418</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
       <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
     </row>
     <row r="11" ht="78" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+    </row>
+    <row r="12" ht="78" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Elective 101_Ms. Son_Room: LH - 611         (75 seats)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="78" customHeight="1">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="78" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="78" customHeight="1">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="78" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="78" customHeight="1">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Teacher load summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Teacher</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Taught timeslots</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ms. Son</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Vạn Lịch/ Bích Huệ</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Tuấn</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B15"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B7"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B16"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B18"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B21"/>
+    <mergeCell ref="B11"/>
+    <mergeCell ref="D13"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Foundation Year 2025/26: Semester 2 - Phase 4 - BFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Interactive export with required blocks on top and shared/program/elective strips below (Study programs: BFA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>PRE-A  (ARC, BFA, CSE)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>C (BFA, ECE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>MONDAY</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Academic English 36_Tuấn_Room: C1 - 232</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="78" customHeight="1">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Business IT2_[BFA]_Tân_Room: LH - 417</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="78" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>German 1_Ms. Son_Room: LH - 417</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="78" customHeight="1">
+      <c r="A11" s="10" t="n"/>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>8.45 - 12.00</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Lunch break</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n"/>
-    </row>
-    <row r="13" ht="78" customHeight="1">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>13.00 - 16.15</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="78" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+    </row>
+    <row r="12" ht="78" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Elective 101_Ms. Son_Room: LH - 611         (75 seats)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="78" customHeight="1">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="78" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>8.45 - 12.00</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Lunch break</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n"/>
-    </row>
-    <row r="16" ht="78" customHeight="1">
-      <c r="A16" s="8" t="n"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>13.00 - 16.15</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="78" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="78" customHeight="1">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="78" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>8.45 - 12.00</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Lunch break</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n"/>
-    </row>
-    <row r="19" ht="78" customHeight="1">
-      <c r="A19" s="8" t="n"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>13.00 - 16.15</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+          <t>8.45 - 12.00</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Lunch break</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="78" customHeight="1">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>13.00 - 16.15</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Teacher load summary</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Teacher</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>Taught timeslots</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ms. Son</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tân</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Tuấn</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B28" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A14:A16"/>
+  <mergeCells count="24">
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B9"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B15"/>
+    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B5"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B7"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="B16"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B18"/>
+    <mergeCell ref="B21"/>
     <mergeCell ref="B11"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B14"/>
-    <mergeCell ref="B8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B17"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B13"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B10"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="D13"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A2:D2"/>
     <mergeCell ref="B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
